--- a/output/yearly_benthic_cover_iteration_26_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_26_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.36076640298826</v>
+        <v>45.30393583454104</v>
       </c>
       <c r="M2" t="n">
-        <v>99.32847589641986</v>
+        <v>100.9990275398436</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>87.8995094924428</v>
+        <v>87.93284964447903</v>
       </c>
       <c r="C3" t="n">
-        <v>45.84065780163287</v>
+        <v>45.88788988821495</v>
       </c>
       <c r="D3" t="n">
-        <v>2.2284691930787</v>
+        <v>2.228519037523759</v>
       </c>
       <c r="E3" t="n">
-        <v>5.649199777883438</v>
+        <v>5.677870844146137</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7428230643595667</v>
+        <v>0.7428396791745865</v>
       </c>
       <c r="G3" t="n">
-        <v>33.9438803402623</v>
+        <v>33.95995219235595</v>
       </c>
       <c r="H3" t="n">
-        <v>34.16986096054006</v>
+        <v>34.17062524203097</v>
       </c>
       <c r="I3" t="n">
-        <v>6.52263200407146</v>
+        <v>6.510294654406461</v>
       </c>
       <c r="J3" t="n">
-        <v>4.642644152247292</v>
+        <v>4.642747994841166</v>
       </c>
       <c r="K3" t="n">
-        <v>12.10049050755718</v>
+        <v>12.06715035552096</v>
       </c>
       <c r="L3" t="n">
-        <v>48.82469518465479</v>
+        <v>48.81125137702976</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7658434938448</v>
+        <v>106.7662916207657</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>86.98120119855575</v>
+        <v>86.96039121758415</v>
       </c>
       <c r="C4" t="n">
-        <v>42.55198519337353</v>
+        <v>42.54093091719533</v>
       </c>
       <c r="D4" t="n">
-        <v>2.18408647322864</v>
+        <v>2.181291869211233</v>
       </c>
       <c r="E4" t="n">
-        <v>6.444501087281332</v>
+        <v>6.463636290167202</v>
       </c>
       <c r="F4" t="n">
-        <v>0.744373614969316</v>
+        <v>0.7443876966027719</v>
       </c>
       <c r="G4" t="n">
-        <v>33.26784598607654</v>
+        <v>33.24026689863916</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24118628858853</v>
+        <v>34.2418340437275</v>
       </c>
       <c r="I4" t="n">
-        <v>5.446872654853165</v>
+        <v>5.436551315468958</v>
       </c>
       <c r="J4" t="n">
-        <v>4.652335093558225</v>
+        <v>4.652423103767325</v>
       </c>
       <c r="K4" t="n">
-        <v>13.01879880144425</v>
+        <v>13.03960878241585</v>
       </c>
       <c r="L4" t="n">
-        <v>44.24803178284691</v>
+        <v>44.23861878221086</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81881577766468</v>
+        <v>99.81915848182203</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>85.7873211858299</v>
+        <v>85.68296342441195</v>
       </c>
       <c r="C5" t="n">
-        <v>42.2034372397818</v>
+        <v>42.10723153304107</v>
       </c>
       <c r="D5" t="n">
-        <v>2.125597674436673</v>
+        <v>2.118499980567398</v>
       </c>
       <c r="E5" t="n">
-        <v>7.029767103512233</v>
+        <v>7.033980173869227</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7456887768758036</v>
+        <v>0.745701988448816</v>
       </c>
       <c r="G5" t="n">
-        <v>32.37694886548527</v>
+        <v>32.28339397069603</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30168373628696</v>
+        <v>34.30229146864553</v>
       </c>
       <c r="I5" t="n">
-        <v>4.547080173759187</v>
+        <v>4.538458414379857</v>
       </c>
       <c r="J5" t="n">
-        <v>4.660554855473772</v>
+        <v>4.6606374278051</v>
       </c>
       <c r="K5" t="n">
-        <v>14.21267881417011</v>
+        <v>14.31703657558805</v>
       </c>
       <c r="L5" t="n">
-        <v>43.43258192785773</v>
+        <v>43.42471657705229</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84869798180964</v>
+        <v>99.84898468568142</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.40893171535245</v>
+        <v>84.08911904185534</v>
       </c>
       <c r="C6" t="n">
-        <v>41.53115186285466</v>
+        <v>41.21807317746651</v>
       </c>
       <c r="D6" t="n">
-        <v>2.058132315511658</v>
+        <v>2.040069707563661</v>
       </c>
       <c r="E6" t="n">
-        <v>7.439131321848466</v>
+        <v>7.404858813943089</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7468062823772379</v>
+        <v>0.7468216401665659</v>
       </c>
       <c r="G6" t="n">
-        <v>31.34932143515055</v>
+        <v>31.08821085725047</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35308898935294</v>
+        <v>34.35379544766203</v>
       </c>
       <c r="I6" t="n">
-        <v>3.794912106253859</v>
+        <v>3.787727324228489</v>
       </c>
       <c r="J6" t="n">
-        <v>4.667539264857736</v>
+        <v>4.667635251041037</v>
       </c>
       <c r="K6" t="n">
-        <v>15.59106828464754</v>
+        <v>15.91088095814466</v>
       </c>
       <c r="L6" t="n">
-        <v>42.75147206989339</v>
+        <v>42.74497757510051</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87369221739559</v>
+        <v>99.87393171071167</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>82.75405252576013</v>
+        <v>82.39083657926531</v>
       </c>
       <c r="C7" t="n">
-        <v>40.46558329116417</v>
+        <v>40.10775179580994</v>
       </c>
       <c r="D7" t="n">
-        <v>1.977266795729169</v>
+        <v>1.957092853624717</v>
       </c>
       <c r="E7" t="n">
-        <v>7.674585805316608</v>
+        <v>7.630422907260722</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7477587966258739</v>
+        <v>0.747776564903918</v>
       </c>
       <c r="G7" t="n">
-        <v>30.11758373122574</v>
+        <v>29.82374331383214</v>
       </c>
       <c r="H7" t="n">
-        <v>34.3969046447902</v>
+        <v>34.39772198558023</v>
       </c>
       <c r="I7" t="n">
-        <v>3.166460273160833</v>
+        <v>3.1604754234141</v>
       </c>
       <c r="J7" t="n">
-        <v>4.673492478911712</v>
+        <v>4.673603530649488</v>
       </c>
       <c r="K7" t="n">
-        <v>17.24594747423987</v>
+        <v>17.60916342073468</v>
       </c>
       <c r="L7" t="n">
-        <v>42.18305500942223</v>
+        <v>42.17787013556014</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89458577482627</v>
+        <v>99.89478535210478</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>87.65823834743817</v>
+        <v>87.30467657363457</v>
       </c>
       <c r="C8" t="n">
-        <v>42.75488013915978</v>
+        <v>42.36057574804262</v>
       </c>
       <c r="D8" t="n">
-        <v>1.981520165528756</v>
+        <v>1.961348828190179</v>
       </c>
       <c r="E8" t="n">
-        <v>9.500368587908497</v>
+        <v>9.434328681120222</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7493673274977896</v>
+        <v>0.7494027105591869</v>
       </c>
       <c r="G8" t="n">
-        <v>30.61559562036378</v>
+        <v>30.30761457741901</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47089706489832</v>
+        <v>34.4725246857226</v>
       </c>
       <c r="I8" t="n">
-        <v>5.656943784379854</v>
+        <v>5.695690149628451</v>
       </c>
       <c r="J8" t="n">
-        <v>4.683545796861185</v>
+        <v>4.683766940994919</v>
       </c>
       <c r="K8" t="n">
-        <v>12.34176165256182</v>
+        <v>12.69532342636543</v>
       </c>
       <c r="L8" t="n">
-        <v>44.71519817329207</v>
+        <v>44.7546564607738</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81183996501366</v>
+        <v>99.81055563518186</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85.58629182166978</v>
+        <v>85.12207996559221</v>
       </c>
       <c r="C9" t="n">
-        <v>41.56059181224985</v>
+        <v>41.06116626558353</v>
       </c>
       <c r="D9" t="n">
-        <v>1.887459452473894</v>
+        <v>1.862160195197276</v>
       </c>
       <c r="E9" t="n">
-        <v>9.836527734887849</v>
+        <v>9.749760324431719</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7507457044668563</v>
+        <v>0.7507981945127998</v>
       </c>
       <c r="G9" t="n">
-        <v>29.16230495759513</v>
+        <v>28.77490870888471</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53430240547539</v>
+        <v>34.53671694758879</v>
       </c>
       <c r="I9" t="n">
-        <v>4.722790913852799</v>
+        <v>4.755246879271909</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692160652917852</v>
+        <v>4.692488715704999</v>
       </c>
       <c r="K9" t="n">
-        <v>14.41370817833022</v>
+        <v>14.87792003440779</v>
       </c>
       <c r="L9" t="n">
-        <v>43.86856268207605</v>
+        <v>43.90270008474123</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84286267265612</v>
+        <v>99.84178638473256</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>83.35518366603721</v>
+        <v>82.79590319239981</v>
       </c>
       <c r="C10" t="n">
-        <v>40.06187287627071</v>
+        <v>39.47190160528851</v>
       </c>
       <c r="D10" t="n">
-        <v>1.787276319121232</v>
+        <v>1.757708788219412</v>
       </c>
       <c r="E10" t="n">
-        <v>9.971398761170647</v>
+        <v>9.864387693335551</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7519291288541287</v>
+        <v>0.7519979102455151</v>
       </c>
       <c r="G10" t="n">
-        <v>27.61441947448796</v>
+        <v>27.16088016931311</v>
       </c>
       <c r="H10" t="n">
-        <v>34.58873992728991</v>
+        <v>34.5919038712937</v>
       </c>
       <c r="I10" t="n">
-        <v>3.941862999775031</v>
+        <v>3.969037820958047</v>
       </c>
       <c r="J10" t="n">
-        <v>4.699557055338304</v>
+        <v>4.69998693903447</v>
       </c>
       <c r="K10" t="n">
-        <v>16.64481633396279</v>
+        <v>17.20409680760021</v>
       </c>
       <c r="L10" t="n">
-        <v>43.16212215327057</v>
+        <v>43.19191139602038</v>
       </c>
       <c r="M10" t="n">
-        <v>99.86881136350407</v>
+        <v>99.86790980890909</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>81.06660210413034</v>
+        <v>80.30925089096348</v>
       </c>
       <c r="C11" t="n">
-        <v>38.38392309391808</v>
+        <v>37.59957751258813</v>
       </c>
       <c r="D11" t="n">
-        <v>1.685666775635422</v>
+        <v>1.647271009205354</v>
       </c>
       <c r="E11" t="n">
-        <v>9.952730099076442</v>
+        <v>9.796616036222453</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7529461288712561</v>
+        <v>0.7530316957017573</v>
       </c>
       <c r="G11" t="n">
-        <v>26.04449515645751</v>
+        <v>25.45434760711061</v>
       </c>
       <c r="H11" t="n">
-        <v>34.63552192807778</v>
+        <v>34.63945800228083</v>
       </c>
       <c r="I11" t="n">
-        <v>3.289328710566584</v>
+        <v>3.312078442306495</v>
       </c>
       <c r="J11" t="n">
-        <v>4.705913305445351</v>
+        <v>4.706448098135984</v>
       </c>
       <c r="K11" t="n">
-        <v>18.93339789586966</v>
+        <v>19.69074910903651</v>
       </c>
       <c r="L11" t="n">
-        <v>42.57318281577408</v>
+        <v>42.5994223277932</v>
       </c>
       <c r="M11" t="n">
-        <v>99.89050380556182</v>
+        <v>99.88974894941785</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>78.7074474066625</v>
+        <v>77.67812251221305</v>
       </c>
       <c r="C12" t="n">
-        <v>36.53353467237368</v>
+        <v>35.48014886425454</v>
       </c>
       <c r="D12" t="n">
-        <v>1.581971321577651</v>
+        <v>1.531621953581666</v>
       </c>
       <c r="E12" t="n">
-        <v>9.797860269546096</v>
+        <v>9.569386746329002</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7538212281188799</v>
+        <v>0.7539246460971065</v>
       </c>
       <c r="G12" t="n">
-        <v>24.44234235259967</v>
+        <v>23.66728813369738</v>
       </c>
       <c r="H12" t="n">
-        <v>34.67577649346847</v>
+        <v>34.6805337204669</v>
       </c>
       <c r="I12" t="n">
-        <v>2.744293065608733</v>
+        <v>2.763338273934083</v>
       </c>
       <c r="J12" t="n">
-        <v>4.711382675742999</v>
+        <v>4.712029038106916</v>
       </c>
       <c r="K12" t="n">
-        <v>21.29255259333753</v>
+        <v>22.32187748778694</v>
       </c>
       <c r="L12" t="n">
-        <v>42.08254249232861</v>
+        <v>42.10597146900557</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90862975803981</v>
+        <v>99.90799782104705</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>76.43177000513029</v>
+        <v>75.13487147800107</v>
       </c>
       <c r="C13" t="n">
-        <v>34.68146958497799</v>
+        <v>33.36276742798401</v>
       </c>
       <c r="D13" t="n">
-        <v>1.482952378774429</v>
+        <v>1.42103776763461</v>
       </c>
       <c r="E13" t="n">
-        <v>9.566123740622608</v>
+        <v>9.262659748626527</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7545738135380361</v>
+        <v>0.7546956593724826</v>
       </c>
       <c r="G13" t="n">
-        <v>22.9124442650824</v>
+        <v>21.95849322793161</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71039542274966</v>
+        <v>34.7160003311342</v>
       </c>
       <c r="I13" t="n">
-        <v>2.289194049750439</v>
+        <v>2.305136872223621</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716086334612725</v>
+        <v>4.716847871078017</v>
       </c>
       <c r="K13" t="n">
-        <v>23.56822999486971</v>
+        <v>24.86512852199893</v>
       </c>
       <c r="L13" t="n">
-        <v>41.67407005721874</v>
+        <v>41.69534465351889</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92376963706644</v>
+        <v>99.92324060350182</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>83.33911314040091</v>
+        <v>82.36445365457877</v>
       </c>
       <c r="C14" t="n">
-        <v>38.9751358349021</v>
+        <v>37.9686720911432</v>
       </c>
       <c r="D14" t="n">
-        <v>1.484707634515514</v>
+        <v>1.422660218113109</v>
       </c>
       <c r="E14" t="n">
-        <v>11.95609290169391</v>
+        <v>11.79683422209717</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7554669440506826</v>
+        <v>0.7555573228423483</v>
       </c>
       <c r="G14" t="n">
-        <v>24.82500020075718</v>
+        <v>24.03697054129765</v>
       </c>
       <c r="H14" t="n">
-        <v>36.63691567838436</v>
+        <v>36.80904335413545</v>
       </c>
       <c r="I14" t="n">
-        <v>2.959261380682501</v>
+        <v>2.821154728328375</v>
       </c>
       <c r="J14" t="n">
-        <v>4.721668400316765</v>
+        <v>4.722233267764678</v>
       </c>
       <c r="K14" t="n">
-        <v>16.66088685959909</v>
+        <v>17.63554634542124</v>
       </c>
       <c r="L14" t="n">
-        <v>44.26545187638674</v>
+        <v>44.30185031720978</v>
       </c>
       <c r="M14" t="n">
-        <v>99.90147457088793</v>
+        <v>99.90606875377421</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>82.73450381674053</v>
+        <v>81.47040547275232</v>
       </c>
       <c r="C15" t="n">
-        <v>38.82766688245168</v>
+        <v>37.50980116812498</v>
       </c>
       <c r="D15" t="n">
-        <v>1.462702161178236</v>
+        <v>1.389857345052205</v>
       </c>
       <c r="E15" t="n">
-        <v>12.19030393699508</v>
+        <v>11.9170339721652</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7562182924015427</v>
+        <v>0.756284784135517</v>
       </c>
       <c r="G15" t="n">
-        <v>24.45705848124554</v>
+        <v>23.4827400346763</v>
       </c>
       <c r="H15" t="n">
-        <v>36.67335285990809</v>
+        <v>36.8444836224899</v>
       </c>
       <c r="I15" t="n">
-        <v>2.468503757502394</v>
+        <v>2.353225813386218</v>
       </c>
       <c r="J15" t="n">
-        <v>4.726364327509641</v>
+        <v>4.726779900846982</v>
       </c>
       <c r="K15" t="n">
-        <v>17.26549618325949</v>
+        <v>18.52959452724768</v>
       </c>
       <c r="L15" t="n">
-        <v>43.82463522926988</v>
+        <v>43.88223889550711</v>
       </c>
       <c r="M15" t="n">
-        <v>99.91779829498104</v>
+        <v>99.92163459087978</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>80.44687458621277</v>
+        <v>78.83907618844481</v>
       </c>
       <c r="C16" t="n">
-        <v>36.9215013853902</v>
+        <v>35.24142377024758</v>
       </c>
       <c r="D16" t="n">
-        <v>1.376073584862761</v>
+        <v>1.291520484152694</v>
       </c>
       <c r="E16" t="n">
-        <v>11.81147306859235</v>
+        <v>11.40097376280495</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7568634110948881</v>
+        <v>0.756912358467424</v>
       </c>
       <c r="G16" t="n">
-        <v>23.00858851016956</v>
+        <v>21.82126092780968</v>
       </c>
       <c r="H16" t="n">
-        <v>36.70463835738322</v>
+        <v>36.87505762408147</v>
       </c>
       <c r="I16" t="n">
-        <v>2.058841334766949</v>
+        <v>1.962648790707189</v>
       </c>
       <c r="J16" t="n">
-        <v>4.73039631934305</v>
+        <v>4.730702240421401</v>
       </c>
       <c r="K16" t="n">
-        <v>19.55312541378724</v>
+        <v>21.1609238115552</v>
       </c>
       <c r="L16" t="n">
-        <v>43.45680365200306</v>
+        <v>43.53228503449206</v>
       </c>
       <c r="M16" t="n">
-        <v>99.93143045118049</v>
+        <v>99.93463261629483</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>82.2967032455087</v>
+        <v>80.73653924635076</v>
       </c>
       <c r="C17" t="n">
-        <v>38.2709308581308</v>
+        <v>36.62215173700649</v>
       </c>
       <c r="D17" t="n">
-        <v>1.377207884968372</v>
+        <v>1.292550082260593</v>
       </c>
       <c r="E17" t="n">
-        <v>12.65031194471644</v>
+        <v>12.24725101037559</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7574872950619824</v>
+        <v>0.7575157678145352</v>
       </c>
       <c r="G17" t="n">
-        <v>23.51747053538045</v>
+        <v>22.35402999858308</v>
       </c>
       <c r="H17" t="n">
-        <v>37.22481006285471</v>
+        <v>37.41982755801218</v>
       </c>
       <c r="I17" t="n">
-        <v>2.035119928389354</v>
+        <v>1.930891280463953</v>
       </c>
       <c r="J17" t="n">
-        <v>4.734295594137389</v>
+        <v>4.734473548840846</v>
       </c>
       <c r="K17" t="n">
-        <v>17.70329675449131</v>
+        <v>19.26346075364921</v>
       </c>
       <c r="L17" t="n">
-        <v>43.9579909288184</v>
+        <v>44.05007573590726</v>
       </c>
       <c r="M17" t="n">
-        <v>99.93221854144051</v>
+        <v>99.93568822656297</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>80.07706004350003</v>
+        <v>78.29804484611141</v>
       </c>
       <c r="C18" t="n">
-        <v>36.36549000372821</v>
+        <v>34.48103180330332</v>
       </c>
       <c r="D18" t="n">
-        <v>1.296703383991498</v>
+        <v>1.20556483868859</v>
       </c>
       <c r="E18" t="n">
-        <v>12.1936948976881</v>
+        <v>11.69140619413943</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7580224277023919</v>
+        <v>0.7580350383534099</v>
       </c>
       <c r="G18" t="n">
-        <v>22.14275997036461</v>
+        <v>20.84966218264372</v>
       </c>
       <c r="H18" t="n">
-        <v>37.25110781204144</v>
+        <v>37.44547852772956</v>
       </c>
       <c r="I18" t="n">
-        <v>1.697131378572039</v>
+        <v>1.61017907484789</v>
       </c>
       <c r="J18" t="n">
-        <v>4.737640173139948</v>
+        <v>4.737718989708813</v>
       </c>
       <c r="K18" t="n">
-        <v>19.92293995649997</v>
+        <v>21.70195515388857</v>
       </c>
       <c r="L18" t="n">
-        <v>43.65503893064989</v>
+        <v>43.76337717390632</v>
       </c>
       <c r="M18" t="n">
-        <v>99.94346889087808</v>
+        <v>99.94636413109822</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>79.24305555126531</v>
+        <v>77.39171500050487</v>
       </c>
       <c r="C19" t="n">
-        <v>35.79288887898023</v>
+        <v>33.80231898367423</v>
       </c>
       <c r="D19" t="n">
-        <v>1.267107477722808</v>
+        <v>1.173059244898145</v>
       </c>
       <c r="E19" t="n">
-        <v>12.15123949507845</v>
+        <v>11.60311052748236</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7584736517613855</v>
+        <v>0.7584796024354197</v>
       </c>
       <c r="G19" t="n">
-        <v>21.63737450079348</v>
+        <v>20.28749362245723</v>
       </c>
       <c r="H19" t="n">
-        <v>37.27328208479997</v>
+        <v>37.46743914161259</v>
       </c>
       <c r="I19" t="n">
-        <v>1.415118017600562</v>
+        <v>1.361635346397746</v>
       </c>
       <c r="J19" t="n">
-        <v>4.740460323508659</v>
+        <v>4.740497515221374</v>
       </c>
       <c r="K19" t="n">
-        <v>20.75694444873468</v>
+        <v>22.60828499949514</v>
       </c>
       <c r="L19" t="n">
-        <v>43.40302413399142</v>
+        <v>43.54403477491472</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95285746170633</v>
+        <v>99.95463875808409</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>76.79012945977352</v>
+        <v>74.83125808296694</v>
       </c>
       <c r="C20" t="n">
-        <v>33.55781320297552</v>
+        <v>31.45080210006824</v>
       </c>
       <c r="D20" t="n">
-        <v>1.179048729434829</v>
+        <v>1.082764574516989</v>
       </c>
       <c r="E20" t="n">
-        <v>11.50342325371956</v>
+        <v>10.89918823122206</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7588621129464579</v>
+        <v>0.7588631672339841</v>
       </c>
       <c r="G20" t="n">
-        <v>20.13366613486833</v>
+        <v>18.72589086669989</v>
       </c>
       <c r="H20" t="n">
-        <v>37.29237203380028</v>
+        <v>37.48638650776579</v>
       </c>
       <c r="I20" t="n">
-        <v>1.179868989088722</v>
+        <v>1.135269940315805</v>
       </c>
       <c r="J20" t="n">
-        <v>4.742888205915361</v>
+        <v>4.742894795212401</v>
       </c>
       <c r="K20" t="n">
-        <v>23.20987054022646</v>
+        <v>25.16874191703308</v>
       </c>
       <c r="L20" t="n">
-        <v>43.19300742297577</v>
+        <v>43.34263277883209</v>
       </c>
       <c r="M20" t="n">
-        <v>99.96069116617775</v>
+        <v>99.9621767959334</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>82.49196304640634</v>
+        <v>81.06741767511309</v>
       </c>
       <c r="C21" t="n">
-        <v>37.0925873495753</v>
+        <v>35.43176444195885</v>
       </c>
       <c r="D21" t="n">
-        <v>1.179854356469854</v>
+        <v>1.083432261190239</v>
       </c>
       <c r="E21" t="n">
-        <v>13.41219262403076</v>
+        <v>13.01463608071529</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7593806325112421</v>
+        <v>0.7593311201348333</v>
       </c>
       <c r="G21" t="n">
-        <v>21.76650456788537</v>
+        <v>20.59621397413606</v>
       </c>
       <c r="H21" t="n">
-        <v>38.93693476371287</v>
+        <v>39.3682782730782</v>
       </c>
       <c r="I21" t="n">
-        <v>1.690967148600982</v>
+        <v>1.499706465015751</v>
       </c>
       <c r="J21" t="n">
-        <v>4.746128953195263</v>
+        <v>4.74581950084271</v>
       </c>
       <c r="K21" t="n">
-        <v>17.50803695359366</v>
+        <v>18.93258232488692</v>
       </c>
       <c r="L21" t="n">
-        <v>45.34304861269726</v>
+        <v>45.58569382511799</v>
       </c>
       <c r="M21" t="n">
-        <v>99.94367291586622</v>
+        <v>99.95004059196376</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_benthic_cover_iteration_26_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_26_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.30393583454104</v>
+        <v>45.64693698279312</v>
       </c>
       <c r="M2" t="n">
-        <v>100.9990275398436</v>
+        <v>99.27230122689866</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>87.93284964447903</v>
+        <v>87.97182502833762</v>
       </c>
       <c r="C3" t="n">
-        <v>45.88788988821495</v>
+        <v>45.90988342298242</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228519037523759</v>
+        <v>2.228602471400002</v>
       </c>
       <c r="E3" t="n">
-        <v>5.677870844146137</v>
+        <v>5.692546453806477</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7428396791745865</v>
+        <v>0.7428674904666674</v>
       </c>
       <c r="G3" t="n">
-        <v>33.95995219235595</v>
+        <v>33.9671834418871</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17062524203097</v>
+        <v>34.1719045614667</v>
       </c>
       <c r="I3" t="n">
-        <v>6.510294654406461</v>
+        <v>6.525798793894015</v>
       </c>
       <c r="J3" t="n">
-        <v>4.642747994841166</v>
+        <v>4.642921815416671</v>
       </c>
       <c r="K3" t="n">
-        <v>12.06715035552096</v>
+        <v>12.02817497166236</v>
       </c>
       <c r="L3" t="n">
-        <v>48.81125137702976</v>
+        <v>48.82768542453731</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7662916207657</v>
+        <v>106.7657438191821</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>86.96039121758415</v>
+        <v>87.05819962794544</v>
       </c>
       <c r="C4" t="n">
-        <v>42.54093091719533</v>
+        <v>42.62393540076443</v>
       </c>
       <c r="D4" t="n">
-        <v>2.181291869211233</v>
+        <v>2.184543122787031</v>
       </c>
       <c r="E4" t="n">
-        <v>6.463636290167202</v>
+        <v>6.488257224677728</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7443876966027719</v>
+        <v>0.7444175132390486</v>
       </c>
       <c r="G4" t="n">
-        <v>33.24026689863916</v>
+        <v>33.29565408845929</v>
       </c>
       <c r="H4" t="n">
-        <v>34.2418340437275</v>
+        <v>34.24320560899623</v>
       </c>
       <c r="I4" t="n">
-        <v>5.436551315468958</v>
+        <v>5.449512612042057</v>
       </c>
       <c r="J4" t="n">
-        <v>4.652423103767325</v>
+        <v>4.652609457744053</v>
       </c>
       <c r="K4" t="n">
-        <v>13.03960878241585</v>
+        <v>12.94180037205457</v>
       </c>
       <c r="L4" t="n">
-        <v>44.23861878221086</v>
+        <v>44.25299203846171</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81915848182203</v>
+        <v>99.81872781128071</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>85.68296342441195</v>
+        <v>85.80698668118936</v>
       </c>
       <c r="C5" t="n">
-        <v>42.10723153304107</v>
+        <v>42.21853575407955</v>
       </c>
       <c r="D5" t="n">
-        <v>2.118499980567398</v>
+        <v>2.123160500453964</v>
       </c>
       <c r="E5" t="n">
-        <v>7.033980173869227</v>
+        <v>7.064160570237544</v>
       </c>
       <c r="F5" t="n">
-        <v>0.745701988448816</v>
+        <v>0.7457330891845221</v>
       </c>
       <c r="G5" t="n">
-        <v>32.28339397069603</v>
+        <v>32.36009253376822</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30229146864553</v>
+        <v>34.303722102488</v>
       </c>
       <c r="I5" t="n">
-        <v>4.538458414379857</v>
+        <v>4.549286077653864</v>
       </c>
       <c r="J5" t="n">
-        <v>4.6606374278051</v>
+        <v>4.660831807403262</v>
       </c>
       <c r="K5" t="n">
-        <v>14.31703657558805</v>
+        <v>14.19301331881062</v>
       </c>
       <c r="L5" t="n">
-        <v>43.42471657705229</v>
+        <v>43.43707557677534</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84898468568142</v>
+        <v>99.84862464966551</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.08911904185534</v>
+        <v>84.23632017683074</v>
       </c>
       <c r="C6" t="n">
-        <v>41.21807317746651</v>
+        <v>41.35432547784865</v>
       </c>
       <c r="D6" t="n">
-        <v>2.040069707563661</v>
+        <v>2.045965430174602</v>
       </c>
       <c r="E6" t="n">
-        <v>7.404858813943089</v>
+        <v>7.440112414876749</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7468216401665659</v>
+        <v>0.7468534986786604</v>
       </c>
       <c r="G6" t="n">
-        <v>31.08821085725047</v>
+        <v>31.18352598740643</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35379544766203</v>
+        <v>34.35526093921836</v>
       </c>
       <c r="I6" t="n">
-        <v>3.787727324228489</v>
+        <v>3.796767539734317</v>
       </c>
       <c r="J6" t="n">
-        <v>4.667635251041037</v>
+        <v>4.667834366741626</v>
       </c>
       <c r="K6" t="n">
-        <v>15.91088095814466</v>
+        <v>15.76367982316925</v>
       </c>
       <c r="L6" t="n">
-        <v>42.74497757510051</v>
+        <v>42.75562564126948</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87393171071167</v>
+        <v>99.87363094228739</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>82.39083657926531</v>
+        <v>82.44846152737206</v>
       </c>
       <c r="C7" t="n">
-        <v>40.10775179580994</v>
+        <v>40.15592750664083</v>
       </c>
       <c r="D7" t="n">
-        <v>1.957092853624717</v>
+        <v>1.958528935007566</v>
       </c>
       <c r="E7" t="n">
-        <v>7.630422907260722</v>
+        <v>7.650155580112053</v>
       </c>
       <c r="F7" t="n">
-        <v>0.747776564903918</v>
+        <v>0.7478100764038973</v>
       </c>
       <c r="G7" t="n">
-        <v>29.82374331383214</v>
+        <v>29.85086504452025</v>
       </c>
       <c r="H7" t="n">
-        <v>34.39772198558023</v>
+        <v>34.39926351457926</v>
       </c>
       <c r="I7" t="n">
-        <v>3.1604754234141</v>
+        <v>3.168025399224661</v>
       </c>
       <c r="J7" t="n">
-        <v>4.673603530649488</v>
+        <v>4.673812977524357</v>
       </c>
       <c r="K7" t="n">
-        <v>17.60916342073468</v>
+        <v>17.55153847262796</v>
       </c>
       <c r="L7" t="n">
-        <v>42.17787013556014</v>
+        <v>42.18706825573858</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89478535210478</v>
+        <v>99.89453423500737</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>87.30467657363457</v>
+        <v>87.33134195297461</v>
       </c>
       <c r="C8" t="n">
-        <v>42.36057574804262</v>
+        <v>42.49599050081311</v>
       </c>
       <c r="D8" t="n">
-        <v>1.961348828190179</v>
+        <v>1.96270644501424</v>
       </c>
       <c r="E8" t="n">
-        <v>9.434328681120222</v>
+        <v>9.50594208074741</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7494027105591869</v>
+        <v>0.7494051429977217</v>
       </c>
       <c r="G8" t="n">
-        <v>30.30761457741901</v>
+        <v>30.36858008086537</v>
       </c>
       <c r="H8" t="n">
-        <v>34.4725246857226</v>
+        <v>34.47263657789518</v>
       </c>
       <c r="I8" t="n">
-        <v>5.695690149628451</v>
+        <v>5.588289481718938</v>
       </c>
       <c r="J8" t="n">
-        <v>4.683766940994919</v>
+        <v>4.683782143735759</v>
       </c>
       <c r="K8" t="n">
-        <v>12.69532342636543</v>
+        <v>12.66865804702538</v>
       </c>
       <c r="L8" t="n">
-        <v>44.7546564607738</v>
+        <v>44.64947161474029</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81055563518186</v>
+        <v>99.81412016257879</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85.12207996559221</v>
+        <v>85.09182111218473</v>
       </c>
       <c r="C9" t="n">
-        <v>41.06116626558353</v>
+        <v>41.12326422574028</v>
       </c>
       <c r="D9" t="n">
-        <v>1.862160195197276</v>
+        <v>1.861039022488338</v>
       </c>
       <c r="E9" t="n">
-        <v>9.749760324431719</v>
+        <v>9.791107829136122</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7507981945127998</v>
+        <v>0.7507747571600532</v>
       </c>
       <c r="G9" t="n">
-        <v>28.77490870888471</v>
+        <v>28.79549956725313</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53671694758879</v>
+        <v>34.53563882936243</v>
       </c>
       <c r="I9" t="n">
-        <v>4.755246879271909</v>
+        <v>4.665418874534343</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692488715704999</v>
+        <v>4.692342232250331</v>
       </c>
       <c r="K9" t="n">
-        <v>14.87792003440779</v>
+        <v>14.90817888781526</v>
       </c>
       <c r="L9" t="n">
-        <v>43.90270008474123</v>
+        <v>43.81332662306339</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84178638473256</v>
+        <v>99.84476973661891</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>82.79590319239981</v>
+        <v>82.68040082289338</v>
       </c>
       <c r="C10" t="n">
-        <v>39.47190160528851</v>
+        <v>39.43497573043162</v>
       </c>
       <c r="D10" t="n">
-        <v>1.757708788219412</v>
+        <v>1.752834451612762</v>
       </c>
       <c r="E10" t="n">
-        <v>9.864387693335551</v>
+        <v>9.870825114426008</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7519979102455151</v>
+        <v>0.7519533844329914</v>
       </c>
       <c r="G10" t="n">
-        <v>27.16088016931311</v>
+        <v>27.12127101203649</v>
       </c>
       <c r="H10" t="n">
-        <v>34.5919038712937</v>
+        <v>34.58985568391758</v>
       </c>
       <c r="I10" t="n">
-        <v>3.969037820958047</v>
+        <v>3.893952523761363</v>
       </c>
       <c r="J10" t="n">
-        <v>4.69998693903447</v>
+        <v>4.699708652706195</v>
       </c>
       <c r="K10" t="n">
-        <v>17.20409680760021</v>
+        <v>17.31959917710661</v>
       </c>
       <c r="L10" t="n">
-        <v>43.19191139602038</v>
+        <v>43.11583012372471</v>
       </c>
       <c r="M10" t="n">
-        <v>99.86790980890909</v>
+        <v>99.87040503126293</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>80.30925089096348</v>
+        <v>80.10190840163338</v>
       </c>
       <c r="C11" t="n">
-        <v>37.59957751258813</v>
+        <v>37.45921828065953</v>
       </c>
       <c r="D11" t="n">
-        <v>1.647271009205354</v>
+        <v>1.63839493779567</v>
       </c>
       <c r="E11" t="n">
-        <v>9.796616036222453</v>
+        <v>9.767934134919415</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7530316957017573</v>
+        <v>0.7529701551992224</v>
       </c>
       <c r="G11" t="n">
-        <v>25.45434760711061</v>
+        <v>25.35057038148731</v>
       </c>
       <c r="H11" t="n">
-        <v>34.63945800228083</v>
+        <v>34.6366271391642</v>
       </c>
       <c r="I11" t="n">
-        <v>3.312078442306495</v>
+        <v>3.24934818307242</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706448098135984</v>
+        <v>4.706063469995138</v>
       </c>
       <c r="K11" t="n">
-        <v>19.69074910903651</v>
+        <v>19.89809159836663</v>
       </c>
       <c r="L11" t="n">
-        <v>42.5994223277932</v>
+        <v>42.53452477309158</v>
       </c>
       <c r="M11" t="n">
-        <v>99.88974894941785</v>
+        <v>99.89183465211774</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>77.67812251221305</v>
+        <v>77.53278187901994</v>
       </c>
       <c r="C12" t="n">
-        <v>35.48014886425454</v>
+        <v>35.39204144554823</v>
       </c>
       <c r="D12" t="n">
-        <v>1.531621953581666</v>
+        <v>1.525655277628756</v>
       </c>
       <c r="E12" t="n">
-        <v>9.569386746329002</v>
+        <v>9.547616774465768</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7539246460971065</v>
+        <v>0.7538477459221258</v>
       </c>
       <c r="G12" t="n">
-        <v>23.66728813369738</v>
+        <v>23.60617126017925</v>
       </c>
       <c r="H12" t="n">
-        <v>34.6805337204669</v>
+        <v>34.67699631241776</v>
       </c>
       <c r="I12" t="n">
-        <v>2.763338273934083</v>
+        <v>2.710946096392981</v>
       </c>
       <c r="J12" t="n">
-        <v>4.712029038106916</v>
+        <v>4.711548412013284</v>
       </c>
       <c r="K12" t="n">
-        <v>22.32187748778694</v>
+        <v>22.46721812098008</v>
       </c>
       <c r="L12" t="n">
-        <v>42.10597146900557</v>
+        <v>42.05048076171969</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90799782104705</v>
+        <v>99.90974032824801</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>75.13487147800107</v>
+        <v>75.04642593991073</v>
       </c>
       <c r="C13" t="n">
-        <v>33.36276742798401</v>
+        <v>33.32345541025242</v>
       </c>
       <c r="D13" t="n">
-        <v>1.42103776763461</v>
+        <v>1.417695401864934</v>
       </c>
       <c r="E13" t="n">
-        <v>9.262659748626527</v>
+        <v>9.24889768178152</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7546956593724826</v>
+        <v>0.7546049414013054</v>
       </c>
       <c r="G13" t="n">
-        <v>21.95849322793161</v>
+        <v>21.93572882545739</v>
       </c>
       <c r="H13" t="n">
-        <v>34.7160003311342</v>
+        <v>34.71182730446002</v>
       </c>
       <c r="I13" t="n">
-        <v>2.305136872223621</v>
+        <v>2.261390901187413</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716847871078017</v>
+        <v>4.716280883758157</v>
       </c>
       <c r="K13" t="n">
-        <v>24.86512852199893</v>
+        <v>24.95357406008925</v>
       </c>
       <c r="L13" t="n">
-        <v>41.69534465351889</v>
+        <v>41.6476664714252</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92324060350182</v>
+        <v>99.92469594176687</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>82.36445365457877</v>
+        <v>82.63131231554713</v>
       </c>
       <c r="C14" t="n">
-        <v>37.9686720911432</v>
+        <v>38.05129940539201</v>
       </c>
       <c r="D14" t="n">
-        <v>1.422660218113109</v>
+        <v>1.419385843691403</v>
       </c>
       <c r="E14" t="n">
-        <v>11.79683422209717</v>
+        <v>11.85623227539231</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7555573228423483</v>
+        <v>0.7555047226616004</v>
       </c>
       <c r="G14" t="n">
-        <v>24.03697054129765</v>
+        <v>24.06554844535114</v>
       </c>
       <c r="H14" t="n">
-        <v>36.80904335413545</v>
+        <v>36.85688098042785</v>
       </c>
       <c r="I14" t="n">
-        <v>2.821154728328375</v>
+        <v>2.955855531387805</v>
       </c>
       <c r="J14" t="n">
-        <v>4.722233267764678</v>
+        <v>4.721904516635001</v>
       </c>
       <c r="K14" t="n">
-        <v>17.63554634542124</v>
+        <v>17.36868768445287</v>
       </c>
       <c r="L14" t="n">
-        <v>44.30185031720978</v>
+        <v>44.48160173666411</v>
       </c>
       <c r="M14" t="n">
-        <v>99.90606875377421</v>
+        <v>99.901588826509</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>81.47040547275232</v>
+        <v>81.85265875887787</v>
       </c>
       <c r="C15" t="n">
-        <v>37.50980116812498</v>
+        <v>37.71416079955345</v>
       </c>
       <c r="D15" t="n">
-        <v>1.389857345052205</v>
+        <v>1.389540855770341</v>
       </c>
       <c r="E15" t="n">
-        <v>11.9170339721652</v>
+        <v>12.03228952839269</v>
       </c>
       <c r="F15" t="n">
-        <v>0.756284784135517</v>
+        <v>0.7562633368462213</v>
       </c>
       <c r="G15" t="n">
-        <v>23.4827400346763</v>
+        <v>23.57393646107144</v>
       </c>
       <c r="H15" t="n">
-        <v>36.8444836224899</v>
+        <v>36.90829642779514</v>
       </c>
       <c r="I15" t="n">
-        <v>2.353225813386218</v>
+        <v>2.465686293713135</v>
       </c>
       <c r="J15" t="n">
-        <v>4.726779900846982</v>
+        <v>4.726645855288881</v>
       </c>
       <c r="K15" t="n">
-        <v>18.52959452724768</v>
+        <v>18.14734124112214</v>
       </c>
       <c r="L15" t="n">
-        <v>43.88223889550711</v>
+        <v>44.05639086123028</v>
       </c>
       <c r="M15" t="n">
-        <v>99.92163459087978</v>
+        <v>99.91789290190587</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>78.83907618844481</v>
+        <v>79.36022713976719</v>
       </c>
       <c r="C16" t="n">
-        <v>35.24142377024758</v>
+        <v>35.60205499265241</v>
       </c>
       <c r="D16" t="n">
-        <v>1.291520484152694</v>
+        <v>1.297045887802328</v>
       </c>
       <c r="E16" t="n">
-        <v>11.40097376280495</v>
+        <v>11.57411084904958</v>
       </c>
       <c r="F16" t="n">
-        <v>0.756912358467424</v>
+        <v>0.7569165883848518</v>
       </c>
       <c r="G16" t="n">
-        <v>21.82126092780968</v>
+        <v>22.0047343114607</v>
       </c>
       <c r="H16" t="n">
-        <v>36.87505762408147</v>
+        <v>36.94017738811015</v>
       </c>
       <c r="I16" t="n">
-        <v>1.962648790707189</v>
+        <v>2.056513437554241</v>
       </c>
       <c r="J16" t="n">
-        <v>4.730702240421401</v>
+        <v>4.730728677405321</v>
       </c>
       <c r="K16" t="n">
-        <v>21.1609238115552</v>
+        <v>20.63977286023282</v>
       </c>
       <c r="L16" t="n">
-        <v>43.53228503449206</v>
+        <v>43.6896808611783</v>
       </c>
       <c r="M16" t="n">
-        <v>99.93463261629483</v>
+        <v>99.93150871406354</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>80.73653924635076</v>
+        <v>81.35030827609181</v>
       </c>
       <c r="C17" t="n">
-        <v>36.62215173700649</v>
+        <v>37.02643605286817</v>
       </c>
       <c r="D17" t="n">
-        <v>1.292550082260593</v>
+        <v>1.298141155911814</v>
       </c>
       <c r="E17" t="n">
-        <v>12.24725101037559</v>
+        <v>12.45302420334813</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7575157678145352</v>
+        <v>0.7575557535898729</v>
       </c>
       <c r="G17" t="n">
-        <v>22.35402999858308</v>
+        <v>22.54898127762291</v>
       </c>
       <c r="H17" t="n">
-        <v>37.41982755801218</v>
+        <v>37.49703633250439</v>
       </c>
       <c r="I17" t="n">
-        <v>1.930891280463953</v>
+        <v>2.060846093177978</v>
       </c>
       <c r="J17" t="n">
-        <v>4.734473548840846</v>
+        <v>4.734723459936704</v>
       </c>
       <c r="K17" t="n">
-        <v>19.26346075364921</v>
+        <v>18.64969172390819</v>
       </c>
       <c r="L17" t="n">
-        <v>44.05007573590726</v>
+        <v>44.25523531271055</v>
       </c>
       <c r="M17" t="n">
-        <v>99.93568822656297</v>
+        <v>99.93136308948691</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>78.29804484611141</v>
+        <v>78.98401160202278</v>
       </c>
       <c r="C18" t="n">
-        <v>34.48103180330332</v>
+        <v>34.97763434045618</v>
       </c>
       <c r="D18" t="n">
-        <v>1.20556483868859</v>
+        <v>1.21439943129512</v>
       </c>
       <c r="E18" t="n">
-        <v>11.69140619413943</v>
+        <v>11.93612889757269</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7580350383534099</v>
+        <v>0.7581052101362882</v>
       </c>
       <c r="G18" t="n">
-        <v>20.84966218264372</v>
+        <v>21.09437014235592</v>
       </c>
       <c r="H18" t="n">
-        <v>37.44547852772956</v>
+        <v>37.52423300019048</v>
       </c>
       <c r="I18" t="n">
-        <v>1.61017907484789</v>
+        <v>1.718617357120469</v>
       </c>
       <c r="J18" t="n">
-        <v>4.737718989708813</v>
+        <v>4.738157563351799</v>
       </c>
       <c r="K18" t="n">
-        <v>21.70195515388857</v>
+        <v>21.01598839797724</v>
       </c>
       <c r="L18" t="n">
-        <v>43.76337717390632</v>
+        <v>43.94913153675608</v>
       </c>
       <c r="M18" t="n">
-        <v>99.94636413109822</v>
+        <v>99.9427542751895</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>77.39171500050487</v>
+        <v>78.11034450253646</v>
       </c>
       <c r="C19" t="n">
-        <v>33.80231898367423</v>
+        <v>34.36803343702936</v>
       </c>
       <c r="D19" t="n">
-        <v>1.173059244898145</v>
+        <v>1.184140995701669</v>
       </c>
       <c r="E19" t="n">
-        <v>11.60311052748236</v>
+        <v>11.87756662573837</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7584796024354197</v>
+        <v>0.758568831172844</v>
       </c>
       <c r="G19" t="n">
-        <v>20.28749362245723</v>
+        <v>20.5687748366531</v>
       </c>
       <c r="H19" t="n">
-        <v>37.46743914161259</v>
+        <v>37.54718103374427</v>
       </c>
       <c r="I19" t="n">
-        <v>1.361635346397746</v>
+        <v>1.433056984695948</v>
       </c>
       <c r="J19" t="n">
-        <v>4.740497515221374</v>
+        <v>4.741055194830273</v>
       </c>
       <c r="K19" t="n">
-        <v>22.60828499949514</v>
+        <v>21.88965549746352</v>
       </c>
       <c r="L19" t="n">
-        <v>43.54403477491472</v>
+        <v>43.694571694476</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95463875808409</v>
+        <v>99.95226062896889</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>74.83125808296694</v>
+        <v>75.52057259854972</v>
       </c>
       <c r="C20" t="n">
-        <v>31.45080210006824</v>
+        <v>31.99831507759812</v>
       </c>
       <c r="D20" t="n">
-        <v>1.082764574516989</v>
+        <v>1.093530628877876</v>
       </c>
       <c r="E20" t="n">
-        <v>10.89918823122206</v>
+        <v>11.16783691233532</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7588631672339841</v>
+        <v>0.7589688861313854</v>
       </c>
       <c r="G20" t="n">
-        <v>18.72589086669989</v>
+        <v>18.99485396081958</v>
       </c>
       <c r="H20" t="n">
-        <v>37.48638650776579</v>
+        <v>37.56698271202912</v>
       </c>
       <c r="I20" t="n">
-        <v>1.135269940315805</v>
+        <v>1.194843960035292</v>
       </c>
       <c r="J20" t="n">
-        <v>4.742894795212401</v>
+        <v>4.743555538321156</v>
       </c>
       <c r="K20" t="n">
-        <v>25.16874191703308</v>
+        <v>24.47942740145027</v>
       </c>
       <c r="L20" t="n">
-        <v>43.34263277883209</v>
+        <v>43.48245038248783</v>
       </c>
       <c r="M20" t="n">
-        <v>99.9621767959334</v>
+        <v>99.96019286153621</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>81.06741767511309</v>
+        <v>81.80634971966853</v>
       </c>
       <c r="C21" t="n">
-        <v>35.43176444195885</v>
+        <v>35.91385751987064</v>
       </c>
       <c r="D21" t="n">
-        <v>1.083432261190239</v>
+        <v>1.094296910682173</v>
       </c>
       <c r="E21" t="n">
-        <v>13.01463608071529</v>
+        <v>13.26967488713931</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7593311201348333</v>
+        <v>0.7595007267877981</v>
       </c>
       <c r="G21" t="n">
-        <v>20.59621397413606</v>
+        <v>20.8155513095948</v>
       </c>
       <c r="H21" t="n">
-        <v>39.3682782730782</v>
+        <v>39.4006943138607</v>
       </c>
       <c r="I21" t="n">
-        <v>1.499706465015751</v>
+        <v>1.719752029180013</v>
       </c>
       <c r="J21" t="n">
-        <v>4.74581950084271</v>
+        <v>4.746879542423736</v>
       </c>
       <c r="K21" t="n">
-        <v>18.93258232488692</v>
+        <v>18.19365028033146</v>
       </c>
       <c r="L21" t="n">
-        <v>45.58569382511799</v>
+        <v>45.83520727405773</v>
       </c>
       <c r="M21" t="n">
-        <v>99.95004059196376</v>
+        <v>99.94271507425984</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_benthic_cover_iteration_26_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_26_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.64693698279312</v>
+        <v>44.7324563430756</v>
       </c>
       <c r="M2" t="n">
-        <v>99.27230122689866</v>
+        <v>92.68734126189997</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>87.97182502833762</v>
+        <v>81.44050694138349</v>
       </c>
       <c r="C3" t="n">
-        <v>45.90988342298242</v>
+        <v>43.19606249693906</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228602471400002</v>
+        <v>2.177826960074643</v>
       </c>
       <c r="E3" t="n">
-        <v>5.692546453806477</v>
+        <v>4.153581365562508</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7428674904666674</v>
+        <v>0.7376072817060711</v>
       </c>
       <c r="G3" t="n">
-        <v>33.9671834418871</v>
+        <v>32.75814719112276</v>
       </c>
       <c r="H3" t="n">
-        <v>34.1719045614667</v>
+        <v>33.92993495847927</v>
       </c>
       <c r="I3" t="n">
-        <v>6.525798793894015</v>
+        <v>3.073363673775297</v>
       </c>
       <c r="J3" t="n">
-        <v>4.642921815416671</v>
+        <v>4.610045510662944</v>
       </c>
       <c r="K3" t="n">
-        <v>12.02817497166236</v>
+        <v>18.5594930586165</v>
       </c>
       <c r="L3" t="n">
-        <v>48.82768542453731</v>
+        <v>45.13333333333333</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7657438191821</v>
+        <v>106.8888888888889</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.05819962794544</v>
+        <v>88.5193162521936</v>
       </c>
       <c r="C4" t="n">
-        <v>42.62393540076443</v>
+        <v>42.78457346986005</v>
       </c>
       <c r="D4" t="n">
-        <v>2.184543122787031</v>
+        <v>2.183552022809537</v>
       </c>
       <c r="E4" t="n">
-        <v>6.488257224677728</v>
+        <v>6.529122386923132</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7444175132390486</v>
+        <v>0.7395463007552875</v>
       </c>
       <c r="G4" t="n">
-        <v>33.29565408845929</v>
+        <v>33.44482467366607</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24320560899623</v>
+        <v>34.01912983474323</v>
       </c>
       <c r="I4" t="n">
-        <v>5.449512612042057</v>
+        <v>6.980976653575806</v>
       </c>
       <c r="J4" t="n">
-        <v>4.652609457744053</v>
+        <v>4.622164379720546</v>
       </c>
       <c r="K4" t="n">
-        <v>12.94180037205457</v>
+        <v>11.48068374780642</v>
       </c>
       <c r="L4" t="n">
-        <v>44.25299203846171</v>
+        <v>45.50265367545638</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81872781128071</v>
+        <v>99.76791089312283</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>85.80698668118936</v>
+        <v>87.33251255811301</v>
       </c>
       <c r="C5" t="n">
-        <v>42.21853575407955</v>
+        <v>42.67982178084785</v>
       </c>
       <c r="D5" t="n">
-        <v>2.123160500453964</v>
+        <v>2.126803828817855</v>
       </c>
       <c r="E5" t="n">
-        <v>7.064160570237544</v>
+        <v>7.331175212087747</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7457330891845221</v>
+        <v>0.741192068297778</v>
       </c>
       <c r="G5" t="n">
-        <v>32.36009253376822</v>
+        <v>32.57562926234861</v>
       </c>
       <c r="H5" t="n">
-        <v>34.303722102488</v>
+        <v>34.09483514169779</v>
       </c>
       <c r="I5" t="n">
-        <v>4.549286077653864</v>
+        <v>5.830426618002116</v>
       </c>
       <c r="J5" t="n">
-        <v>4.660831807403262</v>
+        <v>4.632450426861111</v>
       </c>
       <c r="K5" t="n">
-        <v>14.19301331881062</v>
+        <v>12.667487441887</v>
       </c>
       <c r="L5" t="n">
-        <v>43.43707557677534</v>
+        <v>44.45877475911028</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84862464966551</v>
+        <v>99.80608398184513</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.23632017683074</v>
+        <v>85.95181229025121</v>
       </c>
       <c r="C6" t="n">
-        <v>41.35432547784865</v>
+        <v>42.20388157841272</v>
       </c>
       <c r="D6" t="n">
-        <v>2.045965430174602</v>
+        <v>2.060826724247363</v>
       </c>
       <c r="E6" t="n">
-        <v>7.440112414876749</v>
+        <v>7.915059777006677</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7468534986786604</v>
+        <v>0.7425913097329231</v>
       </c>
       <c r="G6" t="n">
-        <v>31.18352598740643</v>
+        <v>31.56507733970789</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35526093921836</v>
+        <v>34.15920024771446</v>
       </c>
       <c r="I6" t="n">
-        <v>3.796767539734317</v>
+        <v>4.867861206011133</v>
       </c>
       <c r="J6" t="n">
-        <v>4.667834366741626</v>
+        <v>4.641195685830768</v>
       </c>
       <c r="K6" t="n">
-        <v>15.76367982316925</v>
+        <v>14.04818770974879</v>
       </c>
       <c r="L6" t="n">
-        <v>42.75562564126948</v>
+        <v>43.585974416894</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87363094228739</v>
+        <v>99.8380437050555</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>82.44846152737206</v>
+        <v>84.33925651401353</v>
       </c>
       <c r="C7" t="n">
-        <v>40.15592750664083</v>
+        <v>41.34709120862539</v>
       </c>
       <c r="D7" t="n">
-        <v>1.958528935007566</v>
+        <v>1.984009525123304</v>
       </c>
       <c r="E7" t="n">
-        <v>7.650155580112053</v>
+        <v>8.29720390398599</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7478100764038973</v>
+        <v>0.7437837939217624</v>
       </c>
       <c r="G7" t="n">
-        <v>29.85086504452025</v>
+        <v>30.38849087426586</v>
       </c>
       <c r="H7" t="n">
-        <v>34.39926351457926</v>
+        <v>34.21405452040107</v>
       </c>
       <c r="I7" t="n">
-        <v>3.168025399224661</v>
+        <v>4.063065184304526</v>
       </c>
       <c r="J7" t="n">
-        <v>4.673812977524357</v>
+        <v>4.648648712011014</v>
       </c>
       <c r="K7" t="n">
-        <v>17.55153847262796</v>
+        <v>15.66074348598647</v>
       </c>
       <c r="L7" t="n">
-        <v>42.18706825573858</v>
+        <v>42.8569469385545</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89453423500737</v>
+        <v>99.86478163316636</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>87.33134195297461</v>
+        <v>82.59989613115565</v>
       </c>
       <c r="C8" t="n">
-        <v>42.49599050081311</v>
+        <v>40.2384423233702</v>
       </c>
       <c r="D8" t="n">
-        <v>1.96270644501424</v>
+        <v>1.901756003541287</v>
       </c>
       <c r="E8" t="n">
-        <v>9.50594208074741</v>
+        <v>8.518303255664716</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7494051429977217</v>
+        <v>0.7448014764458288</v>
       </c>
       <c r="G8" t="n">
-        <v>30.36858008086537</v>
+        <v>29.12863785525578</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47263657789518</v>
+        <v>34.26086791650813</v>
       </c>
       <c r="I8" t="n">
-        <v>5.588289481718938</v>
+        <v>3.390520395953458</v>
       </c>
       <c r="J8" t="n">
-        <v>4.683782143735759</v>
+        <v>4.655009227786429</v>
       </c>
       <c r="K8" t="n">
-        <v>12.66865804702538</v>
+        <v>17.40010386884437</v>
       </c>
       <c r="L8" t="n">
-        <v>44.64947161474029</v>
+        <v>42.24859088599919</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81412016257879</v>
+        <v>99.88713707821377</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85.09182111218473</v>
+        <v>80.76074046809791</v>
       </c>
       <c r="C9" t="n">
-        <v>41.12326422574028</v>
+        <v>38.92524853839898</v>
       </c>
       <c r="D9" t="n">
-        <v>1.861039022488338</v>
+        <v>1.815434671054191</v>
       </c>
       <c r="E9" t="n">
-        <v>9.791107829136122</v>
+        <v>8.603110070127975</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7507747571600532</v>
+        <v>0.7456710590754767</v>
       </c>
       <c r="G9" t="n">
-        <v>28.79549956725313</v>
+        <v>27.80647937198159</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53563882936243</v>
+        <v>34.30086871747193</v>
       </c>
       <c r="I9" t="n">
-        <v>4.665418874534343</v>
+        <v>2.828732459165023</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692342232250331</v>
+        <v>4.660444119221729</v>
       </c>
       <c r="K9" t="n">
-        <v>14.90817888781526</v>
+        <v>19.2392595319021</v>
       </c>
       <c r="L9" t="n">
-        <v>43.81332662306339</v>
+        <v>41.7413108075891</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84476973661891</v>
+        <v>99.90581887789017</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>82.68040082289338</v>
+        <v>85.62280556263462</v>
       </c>
       <c r="C10" t="n">
-        <v>39.43497573043162</v>
+        <v>42.32505006114034</v>
       </c>
       <c r="D10" t="n">
-        <v>1.752834451612762</v>
+        <v>1.817415201376116</v>
       </c>
       <c r="E10" t="n">
-        <v>9.870825114426008</v>
+        <v>10.52502605289533</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7519533844329914</v>
+        <v>0.7464845414696535</v>
       </c>
       <c r="G10" t="n">
-        <v>27.12127101203649</v>
+        <v>29.28229835602316</v>
       </c>
       <c r="H10" t="n">
-        <v>34.58985568391758</v>
+        <v>35.78377269070436</v>
       </c>
       <c r="I10" t="n">
-        <v>3.893952523761363</v>
+        <v>2.802280335980676</v>
       </c>
       <c r="J10" t="n">
-        <v>4.699708652706195</v>
+        <v>4.665528384185333</v>
       </c>
       <c r="K10" t="n">
-        <v>17.31959917710661</v>
+        <v>14.37719443736537</v>
       </c>
       <c r="L10" t="n">
-        <v>43.11583012372471</v>
+        <v>43.20444794990308</v>
       </c>
       <c r="M10" t="n">
-        <v>99.87040503126293</v>
+        <v>99.90669244840879</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>80.10190840163338</v>
+        <v>85.32959679328428</v>
       </c>
       <c r="C11" t="n">
-        <v>37.45921828065953</v>
+        <v>42.36053227995139</v>
       </c>
       <c r="D11" t="n">
-        <v>1.63839493779567</v>
+        <v>1.797827954972826</v>
       </c>
       <c r="E11" t="n">
-        <v>9.767934134919415</v>
+        <v>10.85040929207243</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7529701551992224</v>
+        <v>0.7471855159537849</v>
       </c>
       <c r="G11" t="n">
-        <v>25.35057038148731</v>
+        <v>29.00488750378649</v>
       </c>
       <c r="H11" t="n">
-        <v>34.6366271391642</v>
+        <v>35.85555486510574</v>
       </c>
       <c r="I11" t="n">
-        <v>3.24934818307242</v>
+        <v>2.403822186681835</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706063469995138</v>
+        <v>4.669909474711155</v>
       </c>
       <c r="K11" t="n">
-        <v>19.89809159836663</v>
+        <v>14.67040320671572</v>
       </c>
       <c r="L11" t="n">
-        <v>42.53452477309158</v>
+        <v>42.88901227889287</v>
       </c>
       <c r="M11" t="n">
-        <v>99.89183465211774</v>
+        <v>99.91994776555998</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>77.53278187901994</v>
+        <v>83.42099089893509</v>
       </c>
       <c r="C12" t="n">
-        <v>35.39204144554823</v>
+        <v>40.82556856503105</v>
       </c>
       <c r="D12" t="n">
-        <v>1.525655277628756</v>
+        <v>1.716823100833698</v>
       </c>
       <c r="E12" t="n">
-        <v>9.547616774465768</v>
+        <v>10.69565331881963</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7538477459221258</v>
+        <v>0.747784066320658</v>
       </c>
       <c r="G12" t="n">
-        <v>23.60617126017925</v>
+        <v>27.69801235198613</v>
       </c>
       <c r="H12" t="n">
-        <v>34.67699631241776</v>
+        <v>35.88427779275986</v>
       </c>
       <c r="I12" t="n">
-        <v>2.710946096392981</v>
+        <v>2.004789853710998</v>
       </c>
       <c r="J12" t="n">
-        <v>4.711548412013284</v>
+        <v>4.673650414504112</v>
       </c>
       <c r="K12" t="n">
-        <v>22.46721812098008</v>
+        <v>16.5790091010649</v>
       </c>
       <c r="L12" t="n">
-        <v>42.05048076171969</v>
+        <v>42.5286494953851</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90974032824801</v>
+        <v>99.93322716148106</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>75.04642593991073</v>
+        <v>84.61594475211321</v>
       </c>
       <c r="C13" t="n">
-        <v>33.32345541025242</v>
+        <v>41.82676424518949</v>
       </c>
       <c r="D13" t="n">
-        <v>1.417695401864934</v>
+        <v>1.718067723643783</v>
       </c>
       <c r="E13" t="n">
-        <v>9.24889768178152</v>
+        <v>11.34136125726885</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7546049414013054</v>
+        <v>0.7483261775640988</v>
       </c>
       <c r="G13" t="n">
-        <v>21.93572882545739</v>
+        <v>28.04933168944704</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71182730446002</v>
+        <v>36.24153182010935</v>
       </c>
       <c r="I13" t="n">
-        <v>2.261390901187413</v>
+        <v>1.840287474304455</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716280883758157</v>
+        <v>4.677038609775618</v>
       </c>
       <c r="K13" t="n">
-        <v>24.95357406008925</v>
+        <v>15.38405524788682</v>
       </c>
       <c r="L13" t="n">
-        <v>41.6476664714252</v>
+        <v>42.72788202986947</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92469594176687</v>
+        <v>99.93870152294578</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>82.63131231554713</v>
+        <v>82.72282101905996</v>
       </c>
       <c r="C14" t="n">
-        <v>38.05129940539201</v>
+        <v>40.21955859741285</v>
       </c>
       <c r="D14" t="n">
-        <v>1.419385843691403</v>
+        <v>1.639961400337298</v>
       </c>
       <c r="E14" t="n">
-        <v>11.85623227539231</v>
+        <v>11.08151693164417</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7555047226616004</v>
+        <v>0.7487888964534054</v>
       </c>
       <c r="G14" t="n">
-        <v>24.06554844535114</v>
+        <v>26.77416067068165</v>
       </c>
       <c r="H14" t="n">
-        <v>36.85688098042785</v>
+        <v>36.26394135468578</v>
       </c>
       <c r="I14" t="n">
-        <v>2.955855531387805</v>
+        <v>1.534521162423882</v>
       </c>
       <c r="J14" t="n">
-        <v>4.721904516635001</v>
+        <v>4.679930602833784</v>
       </c>
       <c r="K14" t="n">
-        <v>17.36868768445287</v>
+        <v>17.27717898094003</v>
       </c>
       <c r="L14" t="n">
-        <v>44.48160173666411</v>
+        <v>42.45214332513868</v>
       </c>
       <c r="M14" t="n">
-        <v>99.901588826509</v>
+        <v>99.94888090349156</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>81.85265875887787</v>
+        <v>81.90030297496496</v>
       </c>
       <c r="C15" t="n">
-        <v>37.71416079955345</v>
+        <v>39.60609996254128</v>
       </c>
       <c r="D15" t="n">
-        <v>1.389540855770341</v>
+        <v>1.605266709838258</v>
       </c>
       <c r="E15" t="n">
-        <v>12.03228952839269</v>
+        <v>11.06498983737393</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7562633368462213</v>
+        <v>0.7491873553172487</v>
       </c>
       <c r="G15" t="n">
-        <v>23.57393646107144</v>
+        <v>26.20773196226826</v>
       </c>
       <c r="H15" t="n">
-        <v>36.90829642779514</v>
+        <v>36.28323876806773</v>
       </c>
       <c r="I15" t="n">
-        <v>2.465686293713135</v>
+        <v>1.307467371366744</v>
       </c>
       <c r="J15" t="n">
-        <v>4.726645855288881</v>
+        <v>4.682420970732805</v>
       </c>
       <c r="K15" t="n">
-        <v>18.14734124112214</v>
+        <v>18.09969702503505</v>
       </c>
       <c r="L15" t="n">
-        <v>44.05639086123028</v>
+        <v>42.25064394613644</v>
       </c>
       <c r="M15" t="n">
-        <v>99.91789290190587</v>
+        <v>99.95644093371276</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>79.36022713976719</v>
+        <v>79.63672656319125</v>
       </c>
       <c r="C16" t="n">
-        <v>35.60205499265241</v>
+        <v>37.54519214349159</v>
       </c>
       <c r="D16" t="n">
-        <v>1.297045887802328</v>
+        <v>1.512493733012904</v>
       </c>
       <c r="E16" t="n">
-        <v>11.57411084904958</v>
+        <v>10.60718781709013</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7569165883848518</v>
+        <v>0.7495291800663716</v>
       </c>
       <c r="G16" t="n">
-        <v>22.0047343114607</v>
+        <v>24.69311180906917</v>
       </c>
       <c r="H16" t="n">
-        <v>36.94017738811015</v>
+        <v>36.29979338408098</v>
       </c>
       <c r="I16" t="n">
-        <v>2.056513437554241</v>
+        <v>1.090053264456868</v>
       </c>
       <c r="J16" t="n">
-        <v>4.730728677405321</v>
+        <v>4.684557375414823</v>
       </c>
       <c r="K16" t="n">
-        <v>20.63977286023282</v>
+        <v>20.36327343680875</v>
       </c>
       <c r="L16" t="n">
-        <v>43.6896808611783</v>
+        <v>42.05521588160615</v>
       </c>
       <c r="M16" t="n">
-        <v>99.93150871406354</v>
+        <v>99.9636814619065</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>81.35030827609181</v>
+        <v>84.32986347109568</v>
       </c>
       <c r="C17" t="n">
-        <v>37.02643605286817</v>
+        <v>40.67837518143752</v>
       </c>
       <c r="D17" t="n">
-        <v>1.298141155911814</v>
+        <v>1.51319203436616</v>
       </c>
       <c r="E17" t="n">
-        <v>12.45302420334813</v>
+        <v>12.26816605564288</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7575557535898729</v>
+        <v>0.7498752292626898</v>
       </c>
       <c r="G17" t="n">
-        <v>22.54898127762291</v>
+        <v>26.16592261068557</v>
       </c>
       <c r="H17" t="n">
-        <v>37.49703633250439</v>
+        <v>37.77796286009962</v>
       </c>
       <c r="I17" t="n">
-        <v>2.060846093177978</v>
+        <v>1.168024498146934</v>
       </c>
       <c r="J17" t="n">
-        <v>4.734723459936704</v>
+        <v>4.686720182891811</v>
       </c>
       <c r="K17" t="n">
-        <v>18.64969172390819</v>
+        <v>15.67013652890434</v>
       </c>
       <c r="L17" t="n">
-        <v>44.25523531271055</v>
+        <v>43.612572106884</v>
       </c>
       <c r="M17" t="n">
-        <v>99.93136308948691</v>
+        <v>99.96108381722586</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>78.98401160202278</v>
+        <v>86.05039595774227</v>
       </c>
       <c r="C18" t="n">
-        <v>34.97763434045618</v>
+        <v>41.41738336057814</v>
       </c>
       <c r="D18" t="n">
-        <v>1.21439943129512</v>
+        <v>1.514423034014539</v>
       </c>
       <c r="E18" t="n">
-        <v>11.93612889757269</v>
+        <v>12.87536027793556</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7581052101362882</v>
+        <v>0.7504852616462777</v>
       </c>
       <c r="G18" t="n">
-        <v>21.09437014235592</v>
+        <v>26.31080831906212</v>
       </c>
       <c r="H18" t="n">
-        <v>37.52423300019048</v>
+        <v>37.80869568048269</v>
       </c>
       <c r="I18" t="n">
-        <v>1.718617357120469</v>
+        <v>2.100090499311847</v>
       </c>
       <c r="J18" t="n">
-        <v>4.738157563351799</v>
+        <v>4.690532885289236</v>
       </c>
       <c r="K18" t="n">
-        <v>21.01598839797724</v>
+        <v>13.94960404225772</v>
       </c>
       <c r="L18" t="n">
-        <v>43.94913153675608</v>
+        <v>44.56306648251341</v>
       </c>
       <c r="M18" t="n">
-        <v>99.9427542751895</v>
+        <v>99.93005388534927</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>78.11034450253646</v>
+        <v>83.5819091651382</v>
       </c>
       <c r="C19" t="n">
-        <v>34.36803343702936</v>
+        <v>39.27426933606994</v>
       </c>
       <c r="D19" t="n">
-        <v>1.184140995701669</v>
+        <v>1.423567005278595</v>
       </c>
       <c r="E19" t="n">
-        <v>11.87756662573837</v>
+        <v>12.39480113663844</v>
       </c>
       <c r="F19" t="n">
-        <v>0.758568831172844</v>
+        <v>0.7510094273615655</v>
       </c>
       <c r="G19" t="n">
-        <v>20.5687748366531</v>
+        <v>24.73232231943642</v>
       </c>
       <c r="H19" t="n">
-        <v>37.54718103374427</v>
+        <v>37.83510262413404</v>
       </c>
       <c r="I19" t="n">
-        <v>1.433056984695948</v>
+        <v>1.751297731279345</v>
       </c>
       <c r="J19" t="n">
-        <v>4.741055194830273</v>
+        <v>4.693808921009785</v>
       </c>
       <c r="K19" t="n">
-        <v>21.88965549746352</v>
+        <v>16.41809083486181</v>
       </c>
       <c r="L19" t="n">
-        <v>43.694571694476</v>
+        <v>44.24930398186513</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95226062896889</v>
+        <v>99.94166415279689</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>75.52057259854972</v>
+        <v>80.97783319710057</v>
       </c>
       <c r="C20" t="n">
-        <v>31.99831507759812</v>
+        <v>36.94085971668842</v>
       </c>
       <c r="D20" t="n">
-        <v>1.093530628877876</v>
+        <v>1.32820382372246</v>
       </c>
       <c r="E20" t="n">
-        <v>11.16783691233532</v>
+        <v>11.80786910371956</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7589688861313854</v>
+        <v>0.7514608649326551</v>
       </c>
       <c r="G20" t="n">
-        <v>18.99485396081958</v>
+        <v>23.07553136059309</v>
       </c>
       <c r="H20" t="n">
-        <v>37.56698271202912</v>
+        <v>37.85784559673635</v>
       </c>
       <c r="I20" t="n">
-        <v>1.194843960035292</v>
+        <v>1.460292041567347</v>
       </c>
       <c r="J20" t="n">
-        <v>4.743555538321156</v>
+        <v>4.696630405829095</v>
       </c>
       <c r="K20" t="n">
-        <v>24.47942740145027</v>
+        <v>19.02216680289943</v>
       </c>
       <c r="L20" t="n">
-        <v>43.48245038248783</v>
+        <v>43.98832632120994</v>
       </c>
       <c r="M20" t="n">
-        <v>99.96019286153621</v>
+        <v>99.9513528407978</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>81.80634971966853</v>
+        <v>78.45807953938071</v>
       </c>
       <c r="C21" t="n">
-        <v>35.91385751987064</v>
+        <v>34.64612983435448</v>
       </c>
       <c r="D21" t="n">
-        <v>1.094296910682173</v>
+        <v>1.236421134313563</v>
       </c>
       <c r="E21" t="n">
-        <v>13.26967488713931</v>
+        <v>11.19483477272606</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7595007267877981</v>
+        <v>0.7518495792213833</v>
       </c>
       <c r="G21" t="n">
-        <v>20.8155513095948</v>
+        <v>21.48094603416418</v>
       </c>
       <c r="H21" t="n">
-        <v>39.4006943138607</v>
+        <v>37.87742863320657</v>
       </c>
       <c r="I21" t="n">
-        <v>1.719752029180013</v>
+        <v>1.217539515615292</v>
       </c>
       <c r="J21" t="n">
-        <v>4.746879542423736</v>
+        <v>4.699059870133646</v>
       </c>
       <c r="K21" t="n">
-        <v>18.19365028033146</v>
+        <v>21.5419204606193</v>
       </c>
       <c r="L21" t="n">
-        <v>45.83520727405773</v>
+        <v>43.77138603720491</v>
       </c>
       <c r="M21" t="n">
-        <v>99.94271507425984</v>
+        <v>99.95943633217868</v>
       </c>
     </row>
   </sheetData>
